--- a/EEC_AI_Feature_Tracker.xlsx
+++ b/EEC_AI_Feature_Tracker.xlsx
@@ -191,7 +191,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -227,11 +227,99 @@
         <color rgb="00999999"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00999999"/>
+      </right>
+      <top style="medium">
+        <color rgb="00999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00999999"/>
+      </right>
+      <top style="medium">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -344,6 +432,10 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -771,6 +863,12 @@
           <t xml:space="preserve">  1. Infrastructure</t>
         </is>
       </c>
+      <c r="B3" s="38" t="n"/>
+      <c r="C3" s="38" t="n"/>
+      <c r="D3" s="38" t="n"/>
+      <c r="E3" s="38" t="n"/>
+      <c r="F3" s="38" t="n"/>
+      <c r="G3" s="39" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="4" t="n">
@@ -1193,6 +1291,12 @@
           <t xml:space="preserve">  2. Document Ingestion</t>
         </is>
       </c>
+      <c r="B17" s="38" t="n"/>
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="38" t="n"/>
+      <c r="E17" s="38" t="n"/>
+      <c r="F17" s="38" t="n"/>
+      <c r="G17" s="39" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="4" t="n">
@@ -1489,7 +1593,7 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E27" s="16" t="inlineStr">
@@ -1499,12 +1603,12 @@
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>NLP extraction of curriculum objectives from ingested text</t>
+          <t>classifier/outcomes.py runs at ingest (ai-service/app/modules/classifier/outcomes.py); legacy docs need re-index</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1628,7 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E28" s="17" t="inlineStr">
@@ -1534,12 +1638,12 @@
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Trigger graph update pipeline after successful embed+upsert</t>
+          <t>teachingMaterialRoutes.js auto-upserts CurriculumMap concepts/learningOutcomes at ingest; no real node/edge graph exists (Question nodes, Student-&gt;Mastery edges are not graph edges -- mastery is a flat MasteryScore collection)</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1663,7 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E29" s="16" t="inlineStr">
@@ -1569,12 +1673,12 @@
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>Tag each chunk with Bloom taxonomy level</t>
+          <t>classifier/bloom.py runs per-chunk + doc-level in documents/service.py, stored in Qdrant payload</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1698,7 @@
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E30" s="16" t="inlineStr">
@@ -1604,12 +1708,12 @@
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Version history with restore capability</t>
+          <t>TeachingMaterial.versions[] + isEnabled exist; no auto-version-on-reupload trigger or browse/restore UI</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1733,7 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -1639,12 +1743,12 @@
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>ML/NLP to suggest topic tags from text</t>
+          <t>classifier/topic.py::detect_topic wired into documents/service.py at ingest (verified: imported + called)</t>
         </is>
       </c>
     </row>
@@ -1654,6 +1758,12 @@
           <t xml:space="preserve">  3. AI Orchestrator</t>
         </is>
       </c>
+      <c r="B32" s="38" t="n"/>
+      <c r="C32" s="38" t="n"/>
+      <c r="D32" s="38" t="n"/>
+      <c r="E32" s="38" t="n"/>
+      <c r="F32" s="38" t="n"/>
+      <c r="G32" s="39" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="4" t="n">
@@ -1671,7 +1781,7 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E33" s="17" t="inlineStr">
@@ -1681,12 +1791,12 @@
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>Single entry point routing to correct AI engine — architectural requirement</t>
+          <t>POST /orchestrate exists (ai-service/app/modules/orchestrator/), dispatches by task_type (generate/generate_questions/evaluate/summarize_session/class_performance/graph_analyze)</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1831,7 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Refactor all direct ai-service calls in Node to go through orchestrator</t>
+          <t>Only 3 call sites (aiTutorRoutes.js + knowledgeGraphClient.js) use /orchestrate; 15+ Node route files still call individual ai-service endpoints directly (/generate/tutor, /vision/explain-image, /reading/evaluate, /video/understand, etc.)</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1851,7 @@
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E35" s="17" t="inlineStr">
@@ -1751,12 +1861,12 @@
       </c>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>Intent detection → route to chat/quiz/flashcard/summary/eval engine</t>
+          <t>dispatch() correctly routes by task_type for what does go through it -- the gap is item 29's not-yet-universal adoption, not this routing logic</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1886,7 @@
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E36" s="17" t="inlineStr">
@@ -1786,12 +1896,12 @@
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>Each module exposes typed interface; orchestrator is sole consumer</t>
+          <t>Orchestrator itself is a clean dispatcher; loose coupling is not actually realized since most callers bypass it (see item 29)</t>
         </is>
       </c>
     </row>
@@ -1801,6 +1911,12 @@
           <t xml:space="preserve">  4. RAG Engine</t>
         </is>
       </c>
+      <c r="B37" s="38" t="n"/>
+      <c r="C37" s="38" t="n"/>
+      <c r="D37" s="38" t="n"/>
+      <c r="E37" s="38" t="n"/>
+      <c r="F37" s="38" t="n"/>
+      <c r="G37" s="39" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="4" t="n">
@@ -1973,7 +2089,7 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E43" s="16" t="inlineStr">
@@ -1983,12 +2099,12 @@
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>Add BM25 lexical layer; merge/rerank with vector scores</t>
+          <t>RRF fusion of vector + keyword hits implemented in retrieval/service.py</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2124,7 @@
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E44" s="17" t="inlineStr">
@@ -2018,12 +2134,12 @@
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Store conversation context in MongoDB, load on session start</t>
+          <t>studentRoute.js auto-triggers /generate/summarize-session after 6+ messages, persists per-subject into StudentMemorySummary, reloaded by studentContextBuilder.js on next session</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2159,7 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr">
@@ -2053,12 +2169,12 @@
       </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>Add org_id + academic_year_id to every Qdrant point and filter</t>
+          <t>retrieval/service.py filters Qdrant by school_id/class_id/section_id/academic_year_id</t>
         </is>
       </c>
     </row>
@@ -2068,6 +2184,12 @@
           <t xml:space="preserve">  5. Knowledge Graph Engine</t>
         </is>
       </c>
+      <c r="B46" s="38" t="n"/>
+      <c r="C46" s="38" t="n"/>
+      <c r="D46" s="38" t="n"/>
+      <c r="E46" s="38" t="n"/>
+      <c r="F46" s="38" t="n"/>
+      <c r="G46" s="39" t="n"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="4" t="n">
@@ -2178,7 +2300,7 @@
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E50" s="17" t="inlineStr">
@@ -2188,12 +2310,12 @@
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>BFS/DFS from weak topic → identify prerequisite chain</t>
+          <t>gapDetectionEngine.js::detectGaps walks CurriculumMap.prerequisites edges for root-cause analysis</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2335,7 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E51" s="17" t="inlineStr">
@@ -2223,12 +2345,12 @@
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>Parse chapter/topic from doc metadata, link to CurriculumMap nodes</t>
+          <t>Same mechanism as item 28 -- CurriculumMap auto-updated at ingest, but not a real node/edge graph</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2370,7 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E52" s="16" t="inlineStr">
@@ -2258,12 +2380,12 @@
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>NER/NLP to extract key concepts and create graph nodes</t>
+          <t>CurriculumMap.concepts populated as string arrays at ingest, not extracted as discrete linked graph nodes</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2405,7 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E53" s="17" t="inlineStr">
@@ -2293,12 +2415,12 @@
       </c>
       <c r="F53" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>Add LearningOutcome model, link to Chapter in CurriculumMap</t>
+          <t>learningOutcomes stored as string arrays on CurriculumMap topics, not as separate linked node objects</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2455,7 @@
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>Map ExamQuestion/PracticeQuestion to CurriculumMap concept nodes</t>
+          <t>No Question-to-concept graph linkage found; questions are not modeled into the curriculum graph structure</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2475,7 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E55" s="17" t="inlineStr">
@@ -2363,12 +2485,12 @@
       </c>
       <c r="F55" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>After each evidence event, update edges in graph</t>
+          <t>MasteryScore is a flat, auto-maintained per-student-per-topic collection (masteryEventService.js) -- functionally equivalent but not modeled as graph edges</t>
         </is>
       </c>
     </row>
@@ -2378,6 +2500,12 @@
           <t xml:space="preserve">  6. Mastery Engine</t>
         </is>
       </c>
+      <c r="B56" s="38" t="n"/>
+      <c r="C56" s="38" t="n"/>
+      <c r="D56" s="38" t="n"/>
+      <c r="E56" s="38" t="n"/>
+      <c r="F56" s="38" t="n"/>
+      <c r="G56" s="39" t="n"/>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="4" t="n">
@@ -2519,7 +2647,7 @@
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr">
@@ -2529,12 +2657,12 @@
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>Server-side grading → evidence event → mastery update (remove browser grading)</t>
+          <t>practiceRoutes.js /student/submit grades server-side and feeds masteryEventService</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2682,7 @@
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E62" s="18" t="inlineStr">
@@ -2564,12 +2692,12 @@
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>Wire exam/practice results to mastery engine via evidence adapter</t>
+          <t>longAnswerAssessmentRoutes.js calls applyMastery() right after evaluation</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2717,7 @@
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E63" s="17" t="inlineStr">
@@ -2599,12 +2727,12 @@
       </c>
       <c r="F63" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>Mount baselineRoutes.js (currently not mounted) + wire to mastery</t>
+          <t>baselineRoutes.js is mounted at /api/baseline; submit handler calls masteryEventService.applyAssessment to bootstrap MasteryScore</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2752,7 @@
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E64" s="18" t="inlineStr">
@@ -2634,12 +2762,12 @@
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>Replace $max non-decreasing formula with weighted evidence model</t>
+          <t>masteryEventService::blendScore is a real EMA (previous*0.7+new*0.3, algorithmVersion mastery-ema-v1) replacing the old non-decreasing $max formula -- simpler than the literal accuracy+attempts+time+recency composite described, but genuinely evidence-weighted and can decrease</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2787,7 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E65" s="16" t="inlineStr">
@@ -2669,12 +2797,12 @@
       </c>
       <c r="F65" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>Decay function applied to mastery score if no recent evidence</t>
+          <t>masteryEngine.js::applyKnowledgeDecay + SpacedRepetitionSchedule</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2822,7 @@
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E66" s="16" t="inlineStr">
@@ -2704,12 +2832,12 @@
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>Visualise concept-level mastery with confidence indicator</t>
+          <t>DashboardHome.jsx MasteryTopicsCard shows per-topic mastery</t>
         </is>
       </c>
     </row>
@@ -2719,6 +2847,12 @@
           <t xml:space="preserve">  7. Error Classification</t>
         </is>
       </c>
+      <c r="B67" s="38" t="n"/>
+      <c r="C67" s="38" t="n"/>
+      <c r="D67" s="38" t="n"/>
+      <c r="E67" s="38" t="n"/>
+      <c r="F67" s="38" t="n"/>
+      <c r="G67" s="39" t="n"/>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="4" t="n">
@@ -2736,7 +2870,7 @@
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E68" s="18" t="inlineStr">
@@ -2746,12 +2880,12 @@
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>Define taxonomy; store error_type on every wrong answer</t>
+          <t>StudentMisconception.js has a 5-value errorType taxonomy, evidence[], occurrence counts, auto-resolve (exact label set may differ from literal "Concept/Calculation/Reading/Logic" -- worth a quick diff, substance is there)</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2905,7 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr">
@@ -2781,12 +2915,12 @@
       </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>FastAPI endpoint: given wrong answer + correct → classify error type</t>
+          <t>Implemented in backend/services/misconceptionService.js (Node), not ai-service FastAPI as originally envisioned -- architecturally equivalent, different service boundary</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2940,7 @@
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E70" s="18" t="inlineStr">
@@ -2816,12 +2950,12 @@
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>Call classifier from practice/quiz submission handler</t>
+          <t>practiceRoutes.js and longAnswerAssessmentRoutes.js both route wrong answers to the classifier after evaluation</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2975,7 @@
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr">
@@ -2851,12 +2985,12 @@
       </c>
       <c r="F71" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>New ErrorRecord model: student, topic, error_type, attempt_ref, timestamp</t>
+          <t>StudentMisconception records with evidence[] per student per attempt</t>
         </is>
       </c>
     </row>
@@ -2876,7 +3010,7 @@
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
@@ -2886,12 +3020,12 @@
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>Dashboard panel showing error patterns per student per concept</t>
+          <t>StudentAnalyticsPortal misconceptions tab + GET /api/teacher-analytics/student-misconceptions/:id</t>
         </is>
       </c>
     </row>
@@ -2901,6 +3035,12 @@
           <t xml:space="preserve">  8. Gap Detection Engine</t>
         </is>
       </c>
+      <c r="B73" s="38" t="n"/>
+      <c r="C73" s="38" t="n"/>
+      <c r="D73" s="38" t="n"/>
+      <c r="E73" s="38" t="n"/>
+      <c r="F73" s="38" t="n"/>
+      <c r="G73" s="39" t="n"/>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="4" t="n">
@@ -2918,7 +3058,7 @@
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E74" s="18" t="inlineStr">
@@ -2928,12 +3068,12 @@
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>Walk back from weak topic via prerequisite edges to find root cause</t>
+          <t>gapDetectionEngine.js walks CurriculumMap prerequisite edges</t>
         </is>
       </c>
     </row>
@@ -2953,7 +3093,7 @@
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr">
@@ -2963,12 +3103,12 @@
       </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>Identify which prerequisite is unmastered causing downstream failures</t>
+          <t>Same engine identifies rootCauses</t>
         </is>
       </c>
     </row>
@@ -2988,7 +3128,7 @@
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
@@ -2998,12 +3138,12 @@
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>Persist GapInsight: student, topic, root_cause, confidence, detected_at</t>
+          <t>StudentInsight records generated after gap detection</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3163,7 @@
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr">
@@ -3033,12 +3173,12 @@
       </c>
       <c r="F77" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
         <is>
-          <t>Trigger gap analysis whenever mastery score changes</t>
+          <t>Verified chain: masteryEngine.runWorkflowTriggers -&gt; gapDetectionEngine.runGapDetection whenever mastery changes</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3198,7 @@
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
@@ -3068,12 +3208,12 @@
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>Push notification + dashboard alert when significant gap detected</t>
+          <t>Real-time socket intervention_alert + StudentAnalyticsPortal dashboard</t>
         </is>
       </c>
     </row>
@@ -3083,6 +3223,12 @@
           <t xml:space="preserve">  9. Bloom Engine</t>
         </is>
       </c>
+      <c r="B79" s="38" t="n"/>
+      <c r="C79" s="38" t="n"/>
+      <c r="D79" s="38" t="n"/>
+      <c r="E79" s="38" t="n"/>
+      <c r="F79" s="38" t="n"/>
+      <c r="G79" s="39" t="n"/>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="4" t="n">
@@ -3100,7 +3246,7 @@
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E80" s="16" t="inlineStr">
@@ -3110,12 +3256,12 @@
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>Classify each chunk: Remember/Understand/Apply/Analyse/Evaluate/Create</t>
+          <t>classifier/bloom.py tags chunks per-chunk + doc-level at ingest</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3281,7 @@
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E81" s="16" t="inlineStr">
@@ -3145,12 +3291,12 @@
       </c>
       <c r="F81" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>LLM prompt to include Bloom level; store as question metadata</t>
+          <t>bloom_question mode + aiTeacherRoutes.js bloomLevel param</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3316,7 @@
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E82" s="16" t="inlineStr">
@@ -3180,12 +3326,12 @@
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>Evaluation endpoint returns which Bloom level student demonstrated</t>
+          <t>evaluator/service.py returns bloomLevel on evaluation results</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3366,7 @@
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>Chart showing % of questions/content at each Bloom level per topic</t>
+          <t>No Bloom-distribution chart/report found for teachers</t>
         </is>
       </c>
     </row>
@@ -3230,6 +3376,12 @@
           <t xml:space="preserve">  10. Student Memory Engine</t>
         </is>
       </c>
+      <c r="B84" s="38" t="n"/>
+      <c r="C84" s="38" t="n"/>
+      <c r="D84" s="38" t="n"/>
+      <c r="E84" s="38" t="n"/>
+      <c r="F84" s="38" t="n"/>
+      <c r="G84" s="39" t="n"/>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="4" t="n">
@@ -3340,7 +3492,7 @@
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
@@ -3350,12 +3502,12 @@
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>Persist weak topics in StudentAcademicProfile (separate from language profile)</t>
+          <t>studentContextBuilder.js pulls MasteryScore weak topics (&lt;60%) into tutor context</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3527,7 @@
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E89" s="17" t="inlineStr">
@@ -3385,12 +3537,12 @@
       </c>
       <c r="F89" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>Store error history with concept links, not just wrong-answer counts</t>
+          <t>Approximated via gaps/weakness data, not a discrete per-mistake log</t>
         </is>
       </c>
     </row>
@@ -3425,7 +3577,7 @@
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>Mark chapters as viewed/studied in student learning state</t>
+          <t>No explicit "chapters studied" tracking found in the student memory profile</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3612,7 @@
       </c>
       <c r="G91" s="10" t="inlineStr">
         <is>
-          <t>Record mastered learning outcomes per chapter per student</t>
+          <t>No explicit learning-outcomes-achieved tracking found</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3632,7 @@
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E92" s="17" t="inlineStr">
@@ -3490,12 +3642,12 @@
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>Store summarised session context in MongoDB; load on next session</t>
+          <t>studentRoute.js summarize-session -&gt; StudentMemorySummary -&gt; reloaded by studentContextBuilder.js</t>
         </is>
       </c>
     </row>
@@ -3505,6 +3657,12 @@
           <t xml:space="preserve">  11. AI Tutor Engine</t>
         </is>
       </c>
+      <c r="B93" s="38" t="n"/>
+      <c r="C93" s="38" t="n"/>
+      <c r="D93" s="38" t="n"/>
+      <c r="E93" s="38" t="n"/>
+      <c r="F93" s="38" t="n"/>
+      <c r="G93" s="39" t="n"/>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="4" t="n">
@@ -3708,7 +3866,7 @@
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E100" s="17" t="inlineStr">
@@ -3718,12 +3876,12 @@
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>Load prior session summaries into LLM context on new session start</t>
+          <t>Same mechanism as item 92 (duplicate item across sections)</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3916,7 @@
       </c>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>Adjust vocabulary/tone based on grade level in system prompt</t>
+          <t>No grade-adaptive vocabulary/tone logic found in system prompts</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3936,7 @@
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E102" s="17" t="inlineStr">
@@ -3788,12 +3946,12 @@
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
         <is>
-          <t>Teacher dashboard: view student chat history with their class</t>
+          <t>aiTutorRoutes.js GET /teacher/student-sessions/:studentId exists (school+allocation scoped) but has zero frontend consumers -- backend-only</t>
         </is>
       </c>
     </row>
@@ -3803,6 +3961,12 @@
           <t xml:space="preserve">  12. Question Generator</t>
         </is>
       </c>
+      <c r="B103" s="38" t="n"/>
+      <c r="C103" s="38" t="n"/>
+      <c r="D103" s="38" t="n"/>
+      <c r="E103" s="38" t="n"/>
+      <c r="F103" s="38" t="n"/>
+      <c r="G103" s="39" t="n"/>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="4" t="n">
@@ -3944,7 +4108,7 @@
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E108" s="16" t="inlineStr">
@@ -3954,12 +4118,12 @@
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>Prompt mode + UI for short answer (1-3 sentence) questions</t>
+          <t>Dedicated short_answer prompt mode in chat/service.py MODE_INSTRUCTIONS</t>
         </is>
       </c>
     </row>
@@ -3979,7 +4143,7 @@
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E109" s="16" t="inlineStr">
@@ -3989,12 +4153,12 @@
       </c>
       <c r="F109" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
         <is>
-          <t>Paragraph/essay question generation with rubric</t>
+          <t>Dedicated long_answer prompt mode with markingCriteria+bloomLevel+marks</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4178,7 @@
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E110" s="16" t="inlineStr">
@@ -4024,12 +4188,12 @@
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>Generate questions targeting specific Bloom taxonomy levels</t>
+          <t>aiTeacherRoutes.js /quiz-generate validates bloomLevel against BLOOM_LEVELS</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4213,7 @@
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E111" s="16" t="inlineStr">
@@ -4059,12 +4223,12 @@
       </c>
       <c r="F111" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
         <is>
-          <t>UI to select Easy/Medium/Hard; prompt adjusts accordingly</t>
+          <t>Same route takes difficulty; PracticePaperBuilder.jsx / PracticeQuestions.jsx pass it through</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4248,7 @@
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E112" s="17" t="inlineStr">
@@ -4094,12 +4258,12 @@
       </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G112" s="10" t="inlineStr">
         <is>
-          <t>Save AI-generated questions to ExamQuestion/PracticeQuestion models</t>
+          <t>PracticeQuestions.jsx saves generated questions to PracticeQuestion via /api/practice/teacher/questions; PracticePaperBuilder.jsx saves sets to PracticePaper.questions</t>
         </is>
       </c>
     </row>
@@ -4119,7 +4283,7 @@
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E113" s="17" t="inlineStr">
@@ -4129,12 +4293,12 @@
       </c>
       <c r="F113" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
         <is>
-          <t>Edit flow for teacher to review, modify, approve AI questions</t>
+          <t>AI output lands in an editable form (question/options/explanation) before save; PUT supported for updates</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4318,7 @@
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E114" s="17" t="inlineStr">
@@ -4164,12 +4328,12 @@
       </c>
       <c r="F114" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>Auto-select difficulty tier from current mastery level</t>
+          <t>aiTutorRoutes.js masteryBasedDifficulty looked up from MasteryScore when difficulty is not explicit</t>
         </is>
       </c>
     </row>
@@ -4179,6 +4343,12 @@
           <t xml:space="preserve">  13. Answer Evaluator</t>
         </is>
       </c>
+      <c r="B115" s="38" t="n"/>
+      <c r="C115" s="38" t="n"/>
+      <c r="D115" s="38" t="n"/>
+      <c r="E115" s="38" t="n"/>
+      <c r="F115" s="38" t="n"/>
+      <c r="G115" s="39" t="n"/>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="4" t="n">
@@ -4289,7 +4459,7 @@
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E119" s="18" t="inlineStr">
@@ -4299,12 +4469,12 @@
       </c>
       <c r="F119" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
         <is>
-          <t>Server-side grading of MCQ (remove browser grading)</t>
+          <t>practiceRoutes.js /student/submit re-fetches correctAnswer server-side, never sent to client</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4494,7 @@
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E120" s="17" t="inlineStr">
@@ -4334,12 +4504,12 @@
       </c>
       <c r="F120" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
         <is>
-          <t>LLM evaluate short/long answers against rubric + curriculum</t>
+          <t>longAnswerAssessmentRoutes.js + ai-service evaluator/service.py::evaluate_written, rubric+curriculum grounded</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4529,7 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E121" s="17" t="inlineStr">
@@ -4369,12 +4539,12 @@
       </c>
       <c r="F121" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
         <is>
-          <t>Identify which concepts are absent from student's answer</t>
+          <t>evaluator schemas missingConcepts field, surfaced in submission responses</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4564,7 @@
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E122" s="16" t="inlineStr">
@@ -4404,12 +4574,12 @@
       </c>
       <c r="F122" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
         <is>
-          <t>Evaluator returns confidence level of its assessment</t>
+          <t>confidenceScore field drives needsReview gating (&lt;0.7)</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4599,7 @@
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E123" s="16" t="inlineStr">
@@ -4439,12 +4609,12 @@
       </c>
       <c r="F123" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
         <is>
-          <t>Detect what cognitive level student demonstrated in answer</t>
+          <t>evaluator bloomLevel field on evaluation results</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4634,7 @@
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E124" s="16" t="inlineStr">
@@ -4474,12 +4644,12 @@
       </c>
       <c r="F124" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
         <is>
-          <t>Tag which curriculum learning outcomes the answer addresses</t>
+          <t>evaluator learningOutcomes field (1-2 outcomes per question)</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4669,7 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E125" s="18" t="inlineStr">
@@ -4509,12 +4679,12 @@
       </c>
       <c r="F125" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
         <is>
-          <t>After evaluation, emit learning event → mastery update</t>
+          <t>longAnswerAssessmentRoutes.js calls applyMastery() right after evaluation, flags masteryApplied</t>
         </is>
       </c>
     </row>
@@ -4524,6 +4694,12 @@
           <t xml:space="preserve">  14. Flashcard Generator</t>
         </is>
       </c>
+      <c r="B126" s="38" t="n"/>
+      <c r="C126" s="38" t="n"/>
+      <c r="D126" s="38" t="n"/>
+      <c r="E126" s="38" t="n"/>
+      <c r="F126" s="38" t="n"/>
+      <c r="G126" s="39" t="n"/>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="4" t="n">
@@ -4696,7 +4872,7 @@
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E132" s="17" t="inlineStr">
@@ -4706,12 +4882,12 @@
       </c>
       <c r="F132" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G132" s="10" t="inlineStr">
         <is>
-          <t>POST rating → evidence event → mastery update for that concept</t>
+          <t>Flashcard rating POSTs to /api/student-dashboard/flashcard-result and /api/student-dashboard/spaced-repetition/review</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4907,7 @@
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E133" s="16" t="inlineStr">
@@ -4741,12 +4917,12 @@
       </c>
       <c r="F133" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G133" s="10" t="inlineStr">
         <is>
-          <t>Schedule review reminders based on Got-it/Still-learning history</t>
+          <t>Same call updates SpacedRepetitionSchedule -- note: a SEPARATE SpacedRepetition.js (SM-2, flashcard-level) also exists with a different scale/granularity; genuine duplication between the two schedulers, both real and written-to</t>
         </is>
       </c>
     </row>
@@ -4756,6 +4932,12 @@
           <t xml:space="preserve">  15. Summary Generator</t>
         </is>
       </c>
+      <c r="B134" s="38" t="n"/>
+      <c r="C134" s="38" t="n"/>
+      <c r="D134" s="38" t="n"/>
+      <c r="E134" s="38" t="n"/>
+      <c r="F134" s="38" t="n"/>
+      <c r="G134" s="39" t="n"/>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="4" t="n">
@@ -4856,6 +5038,12 @@
           <t xml:space="preserve">  16. Mindmap Generator</t>
         </is>
       </c>
+      <c r="B138" s="38" t="n"/>
+      <c r="C138" s="38" t="n"/>
+      <c r="D138" s="38" t="n"/>
+      <c r="E138" s="38" t="n"/>
+      <c r="F138" s="38" t="n"/>
+      <c r="G138" s="39" t="n"/>
     </row>
     <row r="139" ht="20" customHeight="1">
       <c r="A139" s="4" t="n">
@@ -4997,7 +5185,7 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E143" s="13" t="inlineStr">
@@ -5007,12 +5195,12 @@
       </c>
       <c r="F143" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G143" s="10" t="inlineStr">
         <is>
-          <t>html2canvas or Puppeteer screenshot → download PDF/PNG</t>
+          <t>Only PNG export exists (html2canvas exportMindMapPng), not PDF</t>
         </is>
       </c>
     </row>
@@ -5022,6 +5210,12 @@
           <t xml:space="preserve">  17. Notes Generator</t>
         </is>
       </c>
+      <c r="B144" s="38" t="n"/>
+      <c r="C144" s="38" t="n"/>
+      <c r="D144" s="38" t="n"/>
+      <c r="E144" s="38" t="n"/>
+      <c r="F144" s="38" t="n"/>
+      <c r="G144" s="39" t="n"/>
     </row>
     <row r="145" ht="20" customHeight="1">
       <c r="A145" s="4" t="n">
@@ -5101,7 +5295,7 @@
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E147" s="16" t="inlineStr">
@@ -5111,12 +5305,12 @@
       </c>
       <c r="F147" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G147" s="10" t="inlineStr">
         <is>
-          <t>Persist note content in MongoDB linked to student + topic</t>
+          <t>AITutorHomeScreen.jsx calls /api/ai-tutor/save-note, persisted to student profile</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5330,7 @@
       </c>
       <c r="D148" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E148" s="13" t="inlineStr">
@@ -5146,12 +5340,12 @@
       </c>
       <c r="F148" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G148" s="10" t="inlineStr">
         <is>
-          <t>Download button → PDF render of note cards</t>
+          <t>Full PDF export exists (AITutorHomeScreen.jsx + components/tutor/NotesUI.jsx)</t>
         </is>
       </c>
     </row>
@@ -5161,6 +5355,12 @@
           <t xml:space="preserve">  18. Recommendation Engine</t>
         </is>
       </c>
+      <c r="B149" s="38" t="n"/>
+      <c r="C149" s="38" t="n"/>
+      <c r="D149" s="38" t="n"/>
+      <c r="E149" s="38" t="n"/>
+      <c r="F149" s="38" t="n"/>
+      <c r="G149" s="39" t="n"/>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="4" t="n">
@@ -5178,7 +5378,7 @@
       </c>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E150" s="18" t="inlineStr">
@@ -5188,12 +5388,12 @@
       </c>
       <c r="F150" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G150" s="10" t="inlineStr">
         <is>
-          <t>Traverse graph from current mastery state to suggest next node</t>
+          <t>recommendationEngine.js reads StudentInsight/MasteryScore/CurriculumMap to suggest next topic</t>
         </is>
       </c>
     </row>
@@ -5213,7 +5413,7 @@
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E151" s="17" t="inlineStr">
@@ -5223,12 +5423,12 @@
       </c>
       <c r="F151" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G151" s="10" t="inlineStr">
         <is>
-          <t>Recommendations change as mastery/gap data updates</t>
+          <t>Same engine is live-data-driven, not static</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5448,7 @@
       </c>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E152" s="17" t="inlineStr">
@@ -5258,12 +5458,12 @@
       </c>
       <c r="F152" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G152" s="10" t="inlineStr">
         <is>
-          <t>Persist reason code + human-readable explanation with each recommendation</t>
+          <t>RecommendationEvent.reason persisted; RecommendationWidget.jsx displays item.reason to the student directly</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5483,7 @@
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E153" s="17" t="inlineStr">
@@ -5293,12 +5493,12 @@
       </c>
       <c r="F153" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G153" s="10" t="inlineStr">
         <is>
-          <t>UI: Accept / Snooze / Reject / Request Alternative buttons</t>
+          <t>recommendationRoutes.js POST /:id/:decision (accept/dismiss/complete) wired to RecommendationWidget.jsx</t>
         </is>
       </c>
     </row>
@@ -5308,6 +5508,12 @@
           <t xml:space="preserve">  19. Prompt Library</t>
         </is>
       </c>
+      <c r="B154" s="38" t="n"/>
+      <c r="C154" s="38" t="n"/>
+      <c r="D154" s="38" t="n"/>
+      <c r="E154" s="38" t="n"/>
+      <c r="F154" s="38" t="n"/>
+      <c r="G154" s="39" t="n"/>
     </row>
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="4" t="n">
@@ -5325,7 +5531,7 @@
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E155" s="17" t="inlineStr">
@@ -5335,12 +5541,12 @@
       </c>
       <c r="F155" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G155" s="10" t="inlineStr">
         <is>
-          <t>Externalise all chat prompts from chat/router.py</t>
+          <t>ai-service/prompts/chat/ populated, wired into chat/service.py::build_prompt as an override layer</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5566,7 @@
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E156" s="17" t="inlineStr">
@@ -5370,12 +5576,12 @@
       </c>
       <c r="F156" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G156" s="10" t="inlineStr">
         <is>
-          <t>Externalise evaluation prompts</t>
+          <t>ai-service/prompts/evaluation/ populated</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5601,7 @@
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E157" s="17" t="inlineStr">
@@ -5405,12 +5611,12 @@
       </c>
       <c r="F157" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G157" s="10" t="inlineStr">
         <is>
-          <t>Externalise question generation prompts</t>
+          <t>ai-service/prompts/question_generation/ populated</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5636,7 @@
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E158" s="17" t="inlineStr">
@@ -5440,12 +5646,12 @@
       </c>
       <c r="F158" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G158" s="10" t="inlineStr">
         <is>
-          <t>Externalise summary prompts</t>
+          <t>ai-service/prompts/summary/ populated</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5671,7 @@
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E159" s="17" t="inlineStr">
@@ -5475,12 +5681,12 @@
       </c>
       <c r="F159" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G159" s="10" t="inlineStr">
         <is>
-          <t>Externalise mindmap prompts</t>
+          <t>ai-service/prompts/mindmap/ populated</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5706,7 @@
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E160" s="17" t="inlineStr">
@@ -5510,12 +5716,12 @@
       </c>
       <c r="F160" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G160" s="10" t="inlineStr">
         <is>
-          <t>Externalise flashcard prompts</t>
+          <t>ai-service/prompts/flashcards/ populated</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5756,7 @@
       </c>
       <c r="G161" s="10" t="inlineStr">
         <is>
-          <t>Externalise recommendation prompts</t>
+          <t>ai-service/prompts/recommendation/ directory is empty</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5776,7 @@
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E162" s="17" t="inlineStr">
@@ -5580,12 +5786,12 @@
       </c>
       <c r="F162" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G162" s="10" t="inlineStr">
         <is>
-          <t>Systematically replace inline prompt strings with library calls</t>
+          <t>loader.py is wired as an override layer over MODE_INSTRUCTIONS; ~48 fully-written inline prompts still remain as the fallback -- nothing was actually moved OUT, only overridable</t>
         </is>
       </c>
     </row>
@@ -5595,6 +5801,12 @@
           <t xml:space="preserve">  20. Language Assessment</t>
         </is>
       </c>
+      <c r="B163" s="38" t="n"/>
+      <c r="C163" s="38" t="n"/>
+      <c r="D163" s="38" t="n"/>
+      <c r="E163" s="38" t="n"/>
+      <c r="F163" s="38" t="n"/>
+      <c r="G163" s="39" t="n"/>
     </row>
     <row r="164" ht="20" customHeight="1">
       <c r="A164" s="4" t="n">
@@ -6013,6 +6225,12 @@
           <t xml:space="preserve">  21. Speech &amp; Pronunciation</t>
         </is>
       </c>
+      <c r="B177" s="38" t="n"/>
+      <c r="C177" s="38" t="n"/>
+      <c r="D177" s="38" t="n"/>
+      <c r="E177" s="38" t="n"/>
+      <c r="F177" s="38" t="n"/>
+      <c r="G177" s="39" t="n"/>
     </row>
     <row r="178" ht="20" customHeight="1">
       <c r="A178" s="4" t="n">
@@ -6183,6 +6401,12 @@
           <t xml:space="preserve">  22. Analytics Engine</t>
         </is>
       </c>
+      <c r="B183" s="38" t="n"/>
+      <c r="C183" s="38" t="n"/>
+      <c r="D183" s="38" t="n"/>
+      <c r="E183" s="38" t="n"/>
+      <c r="F183" s="38" t="n"/>
+      <c r="G183" s="39" t="n"/>
     </row>
     <row r="184" ht="20" customHeight="1">
       <c r="A184" s="4" t="n">
@@ -6262,7 +6486,7 @@
       </c>
       <c r="D186" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E186" s="17" t="inlineStr">
@@ -6272,12 +6496,12 @@
       </c>
       <c r="F186" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G186" s="10" t="inlineStr">
         <is>
-          <t>Grid: students × topics, colour-coded by mastery score</t>
+          <t>StudentAnalyticsPortal.jsx HeatmapSubPanel renders students x topics from /api/teacher-analytics/mastery-heatmap</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6521,7 @@
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E187" s="17" t="inlineStr">
@@ -6307,12 +6531,12 @@
       </c>
       <c r="F187" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G187" s="10" t="inlineStr">
         <is>
-          <t>Evidence-based at-risk detection (not heuristic label)</t>
+          <t>mlEngine.js::computeAtRisk combines assessment-trend + attendance evidence; mlValidationService.js does genuine retrospective backtesting with confusion-matrix accuracy</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6556,7 @@
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E188" s="17" t="inlineStr">
@@ -6342,12 +6566,12 @@
       </c>
       <c r="F188" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G188" s="10" t="inlineStr">
         <is>
-          <t>LLM summarises class mastery/gap data into actionable insight</t>
+          <t>teacherAnalyticsRoutes.js /class-insights + aiTeacherRoutes.js class_performance_summary + adminAnalyticsRoutes.js /generate/admin-insights</t>
         </is>
       </c>
     </row>
@@ -6367,7 +6591,7 @@
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E189" s="16" t="inlineStr">
@@ -6377,12 +6601,12 @@
       </c>
       <c r="F189" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G189" s="10" t="inlineStr">
         <is>
-          <t>Aggregate mastery → school-level weak subject report</t>
+          <t>adminAnalyticsRoutes.js GET /weak-areas</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6626,7 @@
       </c>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E190" s="16" t="inlineStr">
@@ -6412,12 +6636,12 @@
       </c>
       <c r="F190" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G190" s="10" t="inlineStr">
         <is>
-          <t>Single view of student: mastery, gaps, recommendations, language scores</t>
+          <t>developmentProfileService.js exists backend-side but has zero frontend consumers; StudentAnalyticsPortal.jsx is tab-separated (no single combined mastery+gaps+path+language view) and has no language/reading/writing data at all</t>
         </is>
       </c>
     </row>
@@ -6437,7 +6661,7 @@
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E191" s="16" t="inlineStr">
@@ -6447,12 +6671,12 @@
       </c>
       <c r="F191" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G191" s="10" t="inlineStr">
         <is>
-          <t>Compare pre/post mastery for students who received interventions</t>
+          <t>outcomeStudyService.js does real pre/post mastery-delta + Cohen-d analysis (OutcomeStudy model); StudentAnalyticsPortal intervention tab tracks outcomes</t>
         </is>
       </c>
     </row>
@@ -6462,6 +6686,12 @@
           <t xml:space="preserve">  23. Research-Grade Features</t>
         </is>
       </c>
+      <c r="B192" s="38" t="n"/>
+      <c r="C192" s="38" t="n"/>
+      <c r="D192" s="38" t="n"/>
+      <c r="E192" s="38" t="n"/>
+      <c r="F192" s="38" t="n"/>
+      <c r="G192" s="39" t="n"/>
     </row>
     <row r="193" ht="30" customHeight="1">
       <c r="A193" s="4" t="n">
@@ -6479,7 +6709,7 @@
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E193" s="15" t="inlineStr">
@@ -6489,12 +6719,12 @@
       </c>
       <c r="F193" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G193" s="10" t="inlineStr">
         <is>
-          <t>Track student confidence per topic over time (separate from mastery)</t>
+          <t>backend/models/StudentConfidenceCheckin.js + confidenceTrackingService.js + confidenceRoutes.js; wired into quiz/homework-help/practice check-ins; teacher tab + student card. Tests: confidenceTrackingService.test.js</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6744,7 @@
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E194" s="15" t="inlineStr">
@@ -6524,12 +6754,12 @@
       </c>
       <c r="F194" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G194" s="10" t="inlineStr">
         <is>
-          <t>Record hint requests, tutor questions, retry patterns</t>
+          <t>backend/models/HelpSeekingEvent.js + helpSeekingService.js + helpSeekingRoutes.js; detects Homework Help usage + stuck-signals in any mode + misconception-explainer usage; teacher tab + student card. Tests: helpSeekingService.test.js</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6779,7 @@
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E195" s="16" t="inlineStr">
@@ -6559,12 +6789,12 @@
       </c>
       <c r="F195" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G195" s="10" t="inlineStr">
         <is>
-          <t>Delayed recall tests; decay function on mastery over time</t>
+          <t>Decay function + spaced-repetition scheduling live (SpacedRepetitionSchedule.js, ForgettingCurveChart); no actual delayed-recall re-test mechanism exists (confirmed absent codebase-wide)</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6814,7 @@
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E196" s="18" t="inlineStr">
@@ -6594,12 +6824,12 @@
       </c>
       <c r="F196" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G196" s="10" t="inlineStr">
         <is>
-          <t>Misconception taxonomy + hypothesis lifecycle per student per concept</t>
+          <t>StudentMisconception.js: real 5-value errorType taxonomy, evidence[], auto-resolve; missing a numeric confidence field and a teacher validation/correction workflow (separate from longAnswerAssessmentRoutes.js teacherReview)</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6849,7 @@
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E197" s="16" t="inlineStr">
@@ -6629,12 +6859,12 @@
       </c>
       <c r="F197" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G197" s="10" t="inlineStr">
         <is>
-          <t>Separate engagement dimensions; never conflate with mastery</t>
+          <t>engagementScorer.js computes behavioural+situational+emotional dimensions, confirmed never conflated with mastery/accuracy</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6884,7 @@
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E198" s="16" t="inlineStr">
@@ -6664,12 +6894,12 @@
       </c>
       <c r="F198" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G198" s="10" t="inlineStr">
         <is>
-          <t>Compare outcomes of intervened vs non-intervened cohorts</t>
+          <t>outcomeStudyService.js + OutcomeStudy model; same underlying engine as item 191</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6919,7 @@
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E199" s="17" t="inlineStr">
@@ -6699,12 +6929,12 @@
       </c>
       <c r="F199" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G199" s="10" t="inlineStr">
         <is>
-          <t>Evidence threshold triggers teacher notification with context bundle</t>
+          <t>backend/services/escalationService.js + EscalationCase.js + escalationRoutes.js: evidence-threshold-triggered teacher/leadership notification with dedup + audit log</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6954,7 @@
       </c>
       <c r="D200" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E200" s="17" t="inlineStr">
@@ -6734,12 +6964,12 @@
       </c>
       <c r="F200" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G200" s="10" t="inlineStr">
         <is>
-          <t>Goals, accept/reject recommendations, choose modality</t>
+          <t>RecommendationWidget accept/dismiss + learningPathRoutes.js POST /student/adopt-bridge lets a student choose and adopt their own path</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6989,7 @@
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E201" s="17" t="inlineStr">
@@ -6769,12 +6999,12 @@
       </c>
       <c r="F201" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G201" s="10" t="inlineStr">
         <is>
-          <t>Citation display, recommendation reason, confidence indicator</t>
+          <t>aiInteractionLogger.js/AiInteractionLog.js (lineage) + TutorReasoningTrace.jsx "Why this answer?" panel showing model/retrieval/citations to the student</t>
         </is>
       </c>
     </row>
@@ -6794,7 +7024,7 @@
       </c>
       <c r="D202" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E202" s="15" t="inlineStr">
@@ -6804,12 +7034,12 @@
       </c>
       <c r="F202" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G202" s="10" t="inlineStr">
         <is>
-          <t>Optional peer collaboration features; no surveillance</t>
+          <t>backend/services/belongingService.js: belonging score from Alcove peer-community activity; student card + teacher tab</t>
         </is>
       </c>
     </row>
@@ -6829,7 +7059,7 @@
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E203" s="15" t="inlineStr">
@@ -6839,12 +7069,12 @@
       </c>
       <c r="F203" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G203" s="10" t="inlineStr">
         <is>
-          <t>Controlled pilot study design + outcome measurement</t>
+          <t>outcomeStudyService.js does real pre/post mastery-delta + Cohen-d analysis; not a full controlled pilot-study design with randomization/exposure tracking</t>
         </is>
       </c>
     </row>
@@ -6864,7 +7094,7 @@
       </c>
       <c r="D204" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E204" s="13" t="inlineStr">
@@ -6874,12 +7104,12 @@
       </c>
       <c r="F204" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G204" s="10" t="inlineStr">
         <is>
-          <t>Subgroup fairness analysis for quiz, speech, writing evaluation</t>
+          <t>backend/services/equityMonitoringService.js + admin dashboard section; deliberately gender-cohort-only scope (caste/religion/category excluded pending ethical review)</t>
         </is>
       </c>
     </row>
@@ -6899,7 +7129,7 @@
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E205" s="18" t="inlineStr">
@@ -6909,12 +7139,12 @@
       </c>
       <c r="F205" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G205" s="10" t="inlineStr">
         <is>
-          <t>Distress/self-harm/abuse disclosure detection + escalation workflow</t>
+          <t>escalationService.js auto-escalates a MANUAL wellbeing check-in form (mood/stress/behaviorChanges) to leadership/counsellors -- real and tested. But there is ZERO self-harm/abuse/distress DETECTION within open-ended tutor chat, journal entries, or homework help conversations (verified via codebase-wide grep) -- the actual "child protection layer" for AI-generated/AI-received content is genuinely missing</t>
         </is>
       </c>
     </row>
@@ -6934,7 +7164,7 @@
       </c>
       <c r="D206" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E206" s="13" t="inlineStr">
@@ -6944,12 +7174,12 @@
       </c>
       <c r="F206" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G206" s="10" t="inlineStr">
         <is>
-          <t>Privacy-by-design review, DPO sign-off, DPDP compliance</t>
+          <t>aiConsentService.js gates AI personalisation on parentConsentGivenAt -- real but narrower than the full privacy-by-design/DPO/DPDP framework this item describes</t>
         </is>
       </c>
     </row>
@@ -6959,6 +7189,12 @@
           <t xml:space="preserve">  24. Teacher Controls</t>
         </is>
       </c>
+      <c r="B207" s="38" t="n"/>
+      <c r="C207" s="38" t="n"/>
+      <c r="D207" s="38" t="n"/>
+      <c r="E207" s="38" t="n"/>
+      <c r="F207" s="38" t="n"/>
+      <c r="G207" s="39" t="n"/>
     </row>
     <row r="208" ht="20" customHeight="1">
       <c r="A208" s="4" t="n">
@@ -7193,7 +7429,7 @@
       </c>
       <c r="D215" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E215" s="16" t="inlineStr">
@@ -7203,12 +7439,12 @@
       </c>
       <c r="F215" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G215" s="10" t="inlineStr">
         <is>
-          <t>Toggle active/inactive flag on TeachingMaterial; update RAG retrieval filter</t>
+          <t>Backend exists (teachingMaterialRoutes.js PATCH /:id/toggle-enabled) but zero frontend references found -- backend-only</t>
         </is>
       </c>
     </row>
@@ -7228,7 +7464,7 @@
       </c>
       <c r="D216" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E216" s="16" t="inlineStr">
@@ -7238,12 +7474,12 @@
       </c>
       <c r="F216" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G216" s="10" t="inlineStr">
         <is>
-          <t>Button to re-trigger ingest pipeline for a specific document</t>
+          <t>Backend exists (teachingMaterialRoutes.js POST /:id/reindex) but zero frontend references found -- backend-only</t>
         </is>
       </c>
     </row>
@@ -7263,7 +7499,7 @@
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E217" s="17" t="inlineStr">
@@ -7273,12 +7509,12 @@
       </c>
       <c r="F217" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G217" s="10" t="inlineStr">
         <is>
-          <t>Read-only view of student TutorConversation for teacher's class</t>
+          <t>Backend exists (aiTutorRoutes.js GET /teacher/student-sessions/:studentId, allocation-scoped) but zero frontend references found -- backend-only</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7534,7 @@
       </c>
       <c r="D218" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E218" s="17" t="inlineStr">
@@ -7308,12 +7544,12 @@
       </c>
       <c r="F218" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G218" s="10" t="inlineStr">
         <is>
-          <t>Teacher can mark AI response as incorrect + submit correction</t>
+          <t>Full backend lifecycle exists (aiTutorRoutes.js TutorAnswerCorrection: create/withdraw/list, audited) but zero frontend UI found -- backend-only</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7569,7 @@
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E219" s="17" t="inlineStr">
@@ -7343,12 +7579,12 @@
       </c>
       <c r="F219" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G219" s="10" t="inlineStr">
         <is>
-          <t>Dashboard: student → weak topics → root cause gaps</t>
+          <t>StudentAnalyticsPortal.jsx gaps + misconceptions tabs, root-cause reports</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7604,7 @@
       </c>
       <c r="D220" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E220" s="13" t="inlineStr">
@@ -7378,12 +7614,12 @@
       </c>
       <c r="F220" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G220" s="10" t="inlineStr">
         <is>
-          <t>Download as PDF or image from within the UI</t>
+          <t>Notes: full PDF export exists. Mind map: PNG only (html2canvas), not PDF. Flashcards: no export found</t>
         </is>
       </c>
     </row>
@@ -7393,6 +7629,12 @@
           <t xml:space="preserve">  25. Future ML Features</t>
         </is>
       </c>
+      <c r="B221" s="38" t="n"/>
+      <c r="C221" s="38" t="n"/>
+      <c r="D221" s="38" t="n"/>
+      <c r="E221" s="38" t="n"/>
+      <c r="F221" s="38" t="n"/>
+      <c r="G221" s="39" t="n"/>
     </row>
     <row r="222" ht="30" customHeight="1">
       <c r="A222" s="4" t="n">
@@ -7410,7 +7652,7 @@
       </c>
       <c r="D222" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E222" s="15" t="inlineStr">
@@ -7420,12 +7662,12 @@
       </c>
       <c r="F222" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G222" s="10" t="inlineStr">
         <is>
-          <t>Trained ML model on attendance, mastery, engagement signals</t>
+          <t>mlEngine.js computeAtRisk/dropoutRisk (interpretable rule-based band, not a black-box trained model -- deliberate explainability choice) + mlValidationService.js retrospective backtest</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7687,7 @@
       </c>
       <c r="D223" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E223" s="15" t="inlineStr">
@@ -7455,12 +7697,12 @@
       </c>
       <c r="F223" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G223" s="10" t="inlineStr">
         <is>
-          <t>Time-series model predicting exam performance</t>
+          <t>backend/services/forecastValidationService.js backtests learningEvidenceService.js forecastScores against real later outcomes. Tests: forecastValidationService.test.js</t>
         </is>
       </c>
     </row>
@@ -7480,7 +7722,7 @@
       </c>
       <c r="D224" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E224" s="15" t="inlineStr">
@@ -7490,12 +7732,12 @@
       </c>
       <c r="F224" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G224" s="10" t="inlineStr">
         <is>
-          <t>Infer modality preference from usage patterns (not VAK pseudoscience)</t>
+          <t>backend/services/learningStyleService.js: infers dominant style from AiInteractionLog tutor-mode history, compared to self-report. Tests: learningStyleService.test.js</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7757,7 @@
       </c>
       <c r="D225" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E225" s="15" t="inlineStr">
@@ -7525,12 +7767,12 @@
       </c>
       <c r="F225" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G225" s="10" t="inlineStr">
         <is>
-          <t>Early warning from mastery + error patterns before exam</t>
+          <t>Same forecastValidationService.js/forecastScores engine, viewed as pass/fail prediction</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7792,7 @@
       </c>
       <c r="D226" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E226" s="15" t="inlineStr">
@@ -7560,12 +7802,12 @@
       </c>
       <c r="F226" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G226" s="10" t="inlineStr">
         <is>
-          <t>Forgetting curve model per student per concept</t>
+          <t>estimateRetention formula (exponential decay) + ForgettingCurveChart visualize projected decay; not a trained per-student-per-concept forgetting model calibrated against actual delayed-recall outcomes (no recall-test data exists yet -- see item 195)</t>
         </is>
       </c>
     </row>
@@ -7676,6 +7918,12 @@
           <t xml:space="preserve">  P0 — CRITICAL  |  Must complete before AI Portal is production-ready</t>
         </is>
       </c>
+      <c r="B3" s="38" t="n"/>
+      <c r="C3" s="38" t="n"/>
+      <c r="D3" s="38" t="n"/>
+      <c r="E3" s="38" t="n"/>
+      <c r="F3" s="38" t="n"/>
+      <c r="G3" s="39" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="n">
@@ -7693,7 +7941,7 @@
       </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -7708,7 +7956,7 @@
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>Protect every FastAPI endpoint (generation, documents, speech, assessment, memory, admin) with signed service auth + scopes</t>
+          <t>Zero auth on any of 12 ai-service FastAPI routers (admin/assessment/chat/documents/evaluator/knowledge_graph/language_memory/orchestrator/speech/summaries/video/vision); no shared-secret header from Node either -- anyone reaching port 8000 can call any endpoint directly</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7976,7 @@
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -7738,12 +7986,12 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Enforce org, school, academic year, class, section, student scope in MongoDB, Qdrant, Redis, APIs, deletion, prompts, AI logs</t>
+          <t>Mongo (tenantPlugin.js) and Qdrant (school/class/section/academic_year filters) both genuinely enforced; gap is ai-service has no auth of its own (see item 1), so tenant filters are trusted unverified input from an unauthenticated caller</t>
         </is>
       </c>
     </row>
@@ -7763,7 +8011,7 @@
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -7773,12 +8021,12 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Prevent SSRF: restrict URL schemes, hosts, redirects, private IPs, file types, and max download size</t>
+          <t>aiTutorRoutes.js explain-photo + videoUnderstandingRoutes.js both validate (https-only, cloudinary host allowlist, content-type, size cap). teachingMaterialRoutes.js accepts attachment URLs from req.body unvalidated, and ai-service documents/service.py::download_to_temp does a bare requests.get() with no scheme/host allowlist or private-IP block -- real SSRF surface on the main ingestion path</t>
         </is>
       </c>
     </row>
@@ -7798,7 +8046,7 @@
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -7808,12 +8056,12 @@
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>Remove browser grading and arbitrary mastery updates; load questions and correct answers server-side; persist authoritative attempts</t>
+          <t>practiceRoutes.js /student/submit re-fetches questions+correctAnswer server-side and grades there; correctAnswer never sent to client</t>
         </is>
       </c>
     </row>
@@ -7833,7 +8081,7 @@
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -7843,12 +8091,12 @@
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Add immutable LearningEvent for answers, hints, retries, revisions, abandonment, reassessment, reflections, intervention outcomes</t>
+          <t>MasteryEvent.js is genuinely append-only/immutable (blocks save on non-new docs + all update/delete via pre-hooks), created alongside every MasteryScore change in masteryEventService.js</t>
         </is>
       </c>
     </row>
@@ -7868,7 +8116,7 @@
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -7878,12 +8126,12 @@
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>Replace non-decreasing $max score with concept/skill mastery, confidence, evidence count, recency, history, uncertainty, contradictory-evidence handling</t>
+          <t>masteryEventService::blendScore is a real EMA (previous*0.7+new*0.3, algorithmVersion mastery-ema-v1) -- replaces the old non-decreasing $max formula and can decrease. Simpler than a single accuracy+attempts+time+recency composite, but genuinely evidence-weighted</t>
         </is>
       </c>
     </row>
@@ -7903,7 +8151,7 @@
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -7913,12 +8161,12 @@
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Introduce stable curriculum concepts, skills, learning objectives, chapter relationships, and prerequisite edges</t>
+          <t>CurriculumMap.js has real prerequisites:[String] edges per topic; gapDetectionEngine.js::detectGaps walks them for root-cause analysis</t>
         </is>
       </c>
     </row>
@@ -7938,7 +8186,7 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -7948,12 +8196,12 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>Add misconception taxonomy, error classification, repeated-pattern detection, evidence, confidence, teacher validation, resolution tracking</t>
+          <t>StudentMisconception.js has a real 5-value errorType taxonomy, evidence[], occurrence counts, auto-resolve. Missing: numeric confidence field, teacher validation/correction workflow</t>
         </is>
       </c>
     </row>
@@ -7973,7 +8221,7 @@
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -7983,12 +8231,12 @@
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Persist recommendations with evidence, reasons, confidence, alternatives, expiry, student decision, teacher decision, measured outcome</t>
+          <t>RecommendationEvent.js persists reason/explainability/lifecycle status (issued/accepted/dismissed/completed/expired) + baselineMastery/postMastery/masteryDelta. recommendationRoutes.js POST /:id/:decision + RecommendationWidget.jsx wired end-to-end</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8256,7 @@
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -8018,12 +8266,12 @@
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>Implement: answer → error diagnosis → hint → retry → explanation → example → reassessment → mastery update</t>
+          <t>Verified chain: applyAssessment -&gt; masteryEngine.runWorkflowTriggers -&gt; gapDetectionEngine.runGapDetection -&gt; StudentInsight -&gt; recommendationEngine -&gt; student accept/dismiss/complete -&gt; masteryDelta measured. Socratic homework-help chat is a separate track and does not feed structured hint/retry state into this pipeline</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8291,7 @@
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -8058,7 +8306,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Handle distress, bullying, unsafe requests, self-harm, abuse disclosures, sensitive information, and human escalation</t>
+          <t>escalationService.js::assessWellbeing only checks mood/academicStress/socialEngagement/behaviorChanges from a MANUAL wellbeing form -- zero self-harm/abuse/distress detection in open-ended tutor chat, journal entries, or homework help (confirmed via codebase-wide grep)</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8326,7 @@
       </c>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -8088,12 +8336,12 @@
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Add org/year metadata, trusted enrollment filters, tenant-scoped deletion, source attribution, citation display in student UI</t>
+          <t>Retrieval filters by school_id/class_id/section_id/academic_year_id; citations (source_name/material_id/visual_pages) generated in chat/service.py and rendered via TutorVisualSources.jsx / TutorReasoningTrace.jsx</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8361,7 @@
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -8123,12 +8371,12 @@
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Apply teacher subject/class allocations to every analytics, assessment, recommendation, observation, and intervention query</t>
+          <t>buildTeacherAllocationScope used across teacherAnalyticsRoutes, aiTeacherRoutes, escalationRoutes, studentObservationRoutes, attendanceRoutes, learningPathRoutes, longAnswerAssessmentRoutes, progressRoute, readingAssessmentRoutes, writingAssessmentRoutes, practiceRoutes, masteryEngine.js, meetingRoute.js, with dedicated tests. Not exhaustively verified for every single route in the app</t>
         </is>
       </c>
     </row>
@@ -8148,7 +8396,7 @@
       </c>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -8158,12 +8406,12 @@
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Remove hardcoded goals, recommendations, leaderboards, mastery insights, 'weak student' labels, and demo fallbacks</t>
+          <t>No hardcoded/Math.random fallback found in recommendation/mastery/analytics paths; 'weak student' labels are real threshold-derived data. CAVEAT: a FriendsLeaderboard component running on hardcoded mock data DOES exist elsewhere in the student UI -- see 'Gamification safeguards' (row 59) for the contradiction</t>
         </is>
       </c>
     </row>
@@ -8183,7 +8431,7 @@
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -8193,12 +8441,12 @@
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Delete or anonymize all related assessments, conversations, events, vectors, AI logs, files, summaries, derived state (not only 5 collections)</t>
+          <t>deleteSchoolCascade.js covers ~35 core ERP collections but no AI-era models (MasteryScore/MasteryEvent/RecommendationEvent/StudentMisconception/TutorConversation/EscalationCase) or Qdrant vectors. Separate adminUserManagement.js DELETE /students/:id/all-data covers MasteryScore/TutorConversation/Reading+WritingAssessment + PII anonymization + audit log, but misses PracticeAttempt/ExamResult/EscalationCase/StudentMisconception/RecommendationEvent/Qdrant vectors</t>
         </is>
       </c>
     </row>
@@ -8208,6 +8456,12 @@
           <t xml:space="preserve">  P1 — HIGH  |  Core adaptive-learning features</t>
         </is>
       </c>
+      <c r="B19" s="38" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="38" t="n"/>
+      <c r="E19" s="38" t="n"/>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="39" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="4" t="n">
@@ -8240,7 +8494,7 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Persist session goal, selected topic, activities, context version, recommendation, events, completion state, and follow-up</t>
+          <t>No unified session model; state scattered across PracticeAttempt/MasteryEvent/AdaptivePracticeState/SpacedRepetitionSchedule/TutorConversation</t>
         </is>
       </c>
     </row>
@@ -8260,7 +8514,7 @@
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -8270,12 +8524,12 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Maintain historical mastery, gaps, misconceptions, attempts, successful explanations, interventions, retention, and decline over time</t>
+          <t>studentContextBuilder.js aggregates mastery/gaps/StudentMemorySummary/TutorConversation/dev-profile into a real-time context, functioning as a de facto longitudinal view; no single persisted history-timeline model of historical mastery/gaps/misconceptions/retention/decline</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8564,7 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Let students create, edit, pause, complete, and reflect on subject/concept goals</t>
+          <t>No StudentGoal-type model/route found; "learningGoal" only appears as an ephemeral per-request field, not persisted</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8584,7 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -8340,12 +8594,12 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>Allow students to accept, reject, defer, request an alternative, or choose another topic without penalty</t>
+          <t>recommendationRoutes.js POST /:id/:decision (accept/dismiss/complete), RecommendationWidget.jsx calls it directly on every click</t>
         </is>
       </c>
     </row>
@@ -8365,7 +8619,7 @@
       </c>
       <c r="D24" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -8375,12 +8629,12 @@
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Show why activity was recommended, supporting events, confidence, timestamp, prerequisites, and alternatives</t>
+          <t>RecommendationEvent.reason persisted; RecommendationWidget.jsx displays item.reason to the student directly -- real explanation UI, not just a backend field</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8654,7 @@
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -8410,12 +8664,12 @@
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>AI proposes → teacher sees evidence → approves/changes/rejects → intervention occurs → result is measured</t>
+          <t>Individual pieces exist (TutorAnswerCorrection lifecycle, intervention logging+outcome tracking) but no single AI-proposes-to-teacher-approves-to-measured-outcome workflow; TutorAnswerCorrection backend has no frontend UI</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8689,7 @@
       </c>
       <c r="D26" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -8445,12 +8699,12 @@
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Link interventions to triggers, evidence, start/end dates, teacher decisions, reassessment, and measurable outcomes</t>
+          <t>StudentAnalyticsPortal intervention tab has outcome tracking; outcomeStudyService.js does real pre/post mastery-delta + Cohen-d analysis linking interventions to measured outcomes</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8724,7 @@
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -8480,12 +8734,12 @@
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Select items using concept mastery, prerequisite gaps, recency, prior support, difficulty, spacing, and goals — not one percentage</t>
+          <t>AdaptivePracticeState.js + adaptiveDifficultyService.js + practiceRoutes.js /adaptive/start,/adaptive/next -- steps difficulty rung and Bloom level per topic from lastCorrect/consecutiveCorrect/responseMs, not one percentage</t>
         </is>
       </c>
     </row>
@@ -8505,7 +8759,7 @@
       </c>
       <c r="D28" s="23" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -8515,12 +8769,12 @@
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Replace fixed score bands with item-level evidence, successful independence, confidence, and recent contradictory evidence</t>
+          <t>Same mechanism as item 27, plus aiTutorRoutes.js masteryBasedDifficulty override</t>
         </is>
       </c>
     </row>
@@ -8550,12 +8804,12 @@
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>Track hints and retries; gradually adjust help based on demonstrated need</t>
+          <t>Homework Help mode's 7 Socratic rules give a clue after 'I don't know' -- real but static/rule-based, not a tracked hint/retry count that gradually adjusts scaffolding per student over time</t>
         </is>
       </c>
     </row>
@@ -8575,7 +8829,7 @@
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -8585,12 +8839,12 @@
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Unify duplicate schedulers, correct score-scale inconsistencies, and record later recall outcomes</t>
+          <t>SM-2 (SpacedRepetition.js, flashcard-level) and SpacedRepetitionSchedule.js (topic-level) both real and written-to, feeding recommendations/mastery/cron -- CAVEAT: two separate, incompatible scales/granularities exist; genuine duplication that was never unified as the item asks</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8864,7 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -8620,12 +8874,12 @@
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>Secure, validate, and mount existing baseline route; map diagnostic items to concepts and confidence</t>
+          <t>baselineRoutes.js is mounted at /api/baseline; submit handler calls masteryEventService.applyAssessment to map diagnostic items into MasteryScore</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8899,7 @@
       </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -8660,7 +8914,7 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Schedule concept-level follow-up assessments after learning activities and interventions</t>
+          <t>No reassessment logic found beyond ordinary spaced-repetition scheduling</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8934,7 @@
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -8690,12 +8944,12 @@
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>Build versioned, minimal LLM context from trusted evidence instead of invalid risk/mastery summaries</t>
+          <t>studentContextBuilder.js builds a real, evidence-grounded LLM context from MasteryScore/gaps/memory -- not the invalid risk/mastery summaries this item worried about</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8979,12 @@
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Require validated schemas for activities, hints, questions, explanations, citations, safety disposition, generation metadata</t>
+          <t>response_model (Pydantic) used in knowledge_graph/summaries/evaluator/video/vision/documents routers, but the highest-traffic chat/router.py (/generate/tutor,/generate/teacher,/generate/learning-path) returns plain dict -- not schema-validated</t>
         </is>
       </c>
     </row>
@@ -8750,7 +9004,7 @@
       </c>
       <c r="D35" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -8765,7 +9019,7 @@
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>Add policy checks before and after generation; regex prompt cleaning alone is insufficient</t>
+          <t>Only teacher-note-stripping + injection-stripping exist; no toxicity/PII/harmful-content policy check on LLM output before it reaches the student</t>
         </is>
       </c>
     </row>
@@ -8795,12 +9049,12 @@
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>Add capability-specific timeouts, approved fallbacks, failure disclosure, and safe degradation</t>
+          <t>assessment/service.py has real per-request Ollama-&gt;OpenRouter fallback with explicit timeouts (120-180s). Core create_chain (bulk of chat/quiz/flashcards/etc via app/core/llm.py) picks OpenRouter-vs-Ollama statically at startup -- no per-request timeout, no runtime failover if Ollama hangs mid-request</t>
         </is>
       </c>
     </row>
@@ -8810,6 +9064,12 @@
           <t xml:space="preserve">  P2 — HIGH/MEDIUM  |  Complete the student and teacher experience</t>
         </is>
       </c>
+      <c r="B37" s="38" t="n"/>
+      <c r="C37" s="38" t="n"/>
+      <c r="D37" s="38" t="n"/>
+      <c r="E37" s="38" t="n"/>
+      <c r="F37" s="38" t="n"/>
+      <c r="G37" s="39" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="4" t="n">
@@ -8837,12 +9097,12 @@
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>Show concept progress, evidence strength, uncertainty, recent improvement, retention, goals, next steps — not fixed badges</t>
+          <t>DashboardHome.jsx MasteryTopicsCard shows a fixed score%+bar per topic; the separate ConfidenceCalibration card adds self-rating-vs-mastery but not on the mastery card itself -- no evidence-count/uncertainty/recent-trend shown together</t>
         </is>
       </c>
     </row>
@@ -8862,7 +9122,7 @@
       </c>
       <c r="D39" s="23" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -8877,7 +9137,7 @@
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>Add post-activity reflection; feed it into planning without treating self-rating as mastery</t>
+          <t>No reflection model/route/UI found anywhere in the codebase</t>
         </is>
       </c>
     </row>
@@ -8897,7 +9157,7 @@
       </c>
       <c r="D40" s="23" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -8912,7 +9172,7 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Record changed answers, draft lineage, delayed retries, independent corrections, support used</t>
+          <t>No attemptHistory/draft-lineage fields found in any model; no revision-tracking arrays</t>
         </is>
       </c>
     </row>
@@ -8932,7 +9192,7 @@
       </c>
       <c r="D41" s="23" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -8947,7 +9207,7 @@
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>Use hint-first feedback, explanation, example, student revision, comparison, reassessment — not rewriting the answer</t>
+          <t>ai-service assessment/service.py generates a full AI-rewritten improved_version shown directly in WritingScoreCard.jsx -- one-shot submit-score-rewrite, the OPPOSITE of a hint-first/student-revision loop this item asks for</t>
         </is>
       </c>
     </row>
@@ -8982,7 +9242,7 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Add vocabulary, comprehension, inference, perspective-taking, emotional understanding, interest, reading stamina</t>
+          <t>ReadingEvaluationResult schema only has pronunciation/grammar/fluency/confidence/accent/reading_speed -- no vocabulary, comprehension, inference, or perspective-taking fields</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9262,7 @@
       </c>
       <c r="D43" s="23" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -9017,7 +9277,7 @@
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>Feed pronunciation, fluency, listening, speaking evidence into student model with evaluated confidence</t>
+          <t>ReadingAssessment/pronunciation data is never referenced in masteryEngine.js or gapDetectionEngine.js -- collected but not integrated as evidence</t>
         </is>
       </c>
     </row>
@@ -9037,7 +9297,7 @@
       </c>
       <c r="D44" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -9052,7 +9312,7 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Validate models across children, accents, dialects, devices, and background noise; don't treat accent as quality</t>
+          <t>No accent/device/background-noise validation tests found in ai-service/tests or backend/__tests__</t>
         </is>
       </c>
     </row>
@@ -9072,7 +9332,7 @@
       </c>
       <c r="D45" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -9082,12 +9342,12 @@
       </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>Separate session participation from mastery, retention, transfer, and assessment performance</t>
+          <t>engagementScorer.js computes behavioural (time/views/attempt-count)+situational (recency)+emotional (wellbeing) purely -- confirmed it never touches mastery/accuracy scores</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9382,7 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>Measure whether knowledge is recalled after a meaningful delay (delayed recall tests)</t>
+          <t>Only spaced-repetition nudges exist; the 'retention cron' in spacedRepetitionCron.js is actually dataRetentionService (GDPR data-deletion), unrelated. No delayed-recall re-test mechanism</t>
         </is>
       </c>
     </row>
@@ -9157,7 +9417,7 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Assess whether knowledge can be applied to novel questions or real-world situations</t>
+          <t>No novel-question/apply-to-new-context measurement found</t>
         </is>
       </c>
     </row>
@@ -9177,7 +9437,7 @@
       </c>
       <c r="D48" s="23" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -9192,7 +9452,7 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Verified, privacy-limited progress context and appropriate parent-child activities — not surveillance metrics</t>
+          <t>ChildGrowthAnalytics.jsx and AnalyticsPureWhiteDashboard.jsx (parent portal) are raw metric dashboards (score rings, radar charts, subject %) with zero 'recommendation' strings -- surveillance-style, not privacy-limited/action-oriented as this item asks</t>
         </is>
       </c>
     </row>
@@ -9212,7 +9472,7 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -9222,12 +9482,12 @@
       </c>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>Display attempts, misconceptions, support used, mastery changes, recommendation logic, intervention outcomes</t>
+          <t>StudentAnalyticsPortal.jsx (2965 lines) has intervention logs with outcome tracking, misconception reports with root-cause, real-time socket intervention alerts, gaps/forecast/mastery-growth tabs -- rich and already teacher-readable</t>
         </is>
       </c>
     </row>
@@ -9257,12 +9517,12 @@
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>Add concept IDs, difficulty metadata, objectives, answer validation, distractor checks, duplication checks, provenance, teacher review</t>
+          <t>difficulty/bloomLevel/subject-chapter-topic tags/loosely-parsed objectives exist (aiTeacherRoutes.js); no concept IDs, no distractor/duplication checks, minimal provenance (only source:"ai_generated")</t>
         </is>
       </c>
     </row>
@@ -9282,7 +9542,7 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -9292,12 +9552,12 @@
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>Generated questions need draft → validation → approval → publication → versioning → retirement states</t>
+          <t>GeneratedQuestion.js has isApproved (boolean) + teacherEdited -- not a full draft-&gt;validate-&gt;publish-&gt;version-&gt;retire state machine</t>
         </is>
       </c>
     </row>
@@ -9307,6 +9567,12 @@
           <t xml:space="preserve">  P3 — MEDIUM  |  Multimodal, motivation, and real-world learning</t>
         </is>
       </c>
+      <c r="B52" s="38" t="n"/>
+      <c r="C52" s="38" t="n"/>
+      <c r="D52" s="38" t="n"/>
+      <c r="E52" s="38" t="n"/>
+      <c r="F52" s="38" t="n"/>
+      <c r="G52" s="39" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="4" t="n">
@@ -9324,7 +9590,7 @@
       </c>
       <c r="D53" s="23" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -9339,7 +9605,7 @@
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>Let students choose text, audio, visual, interactive, or example-based support where appropriate</t>
+          <t>No text/audio/visual/interactive modality-choice UI found for students</t>
         </is>
       </c>
     </row>
@@ -9374,7 +9640,7 @@
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>Store accessibility and task preferences without assigning permanent 'learning style' labels</t>
+          <t>No accessibility/task-preference storage found (distinct from the learningStyle self-report field, which does exist)</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9675,7 @@
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>Recommend experiments, observations, outdoor tasks, parent reading, peer work, teacher-led activities</t>
+          <t>No offline/real-world activity recommendations found</t>
         </is>
       </c>
     </row>
@@ -9429,7 +9695,7 @@
       </c>
       <c r="D56" s="23" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -9444,7 +9710,7 @@
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>Adapt examples using safe, student-selected interests without collecting unnecessary sensitive data</t>
+          <t>No student-interest field referenced anywhere in ai-service chat/service.py -- examples are not adapted to individual student interests</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9730,7 @@
       </c>
       <c r="D57" s="23" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -9479,7 +9745,7 @@
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>Support planning, goal review, reflection, revision, delayed retry, and independent practice</t>
+          <t>No planning/goal-review/self-regulation support found</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9765,7 @@
       </c>
       <c r="D58" s="23" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -9514,7 +9780,7 @@
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>Emphasize meaningful progress, choice, suitable challenge, reflection, and encouragement</t>
+          <t>No structured motivation/reflection system found; see item 59 for a related, more specific finding</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9800,7 @@
       </c>
       <c r="D59" s="23" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -9549,7 +9815,7 @@
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>Remove excessive leaderboards, pressure, permanent rankings, manipulative streaks, shame-oriented feedback</t>
+          <t>FriendsLeaderboard + a streak badge in AITutorHomeScreen.jsx run on hardcoded mock constants (STUDENT/LEADERBOARD, not even live data) with no opt-out or anti-pressure safeguard logic -- the opposite of what this item asks for, and directly contradicts item 17 ('Remove fake intelligence') being marked Done -- this IS hardcoded fake leaderboard data still present in the student UI</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9850,7 @@
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>Show previous suggestions, student choices, results, and alternatives without forcing a fixed path</t>
+          <t>RecommendationWidget.jsx only shows current recommendations with accept/dismiss; no history-of-past-recommendations view</t>
         </is>
       </c>
     </row>
@@ -9604,7 +9870,7 @@
       </c>
       <c r="D61" s="23" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -9619,7 +9885,7 @@
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>Persist active goals, unfinished activities, prior support, safe conversation context through a learning session model</t>
+          <t>No persisted active-goal/unfinished-activity state found across sessions</t>
         </is>
       </c>
     </row>
@@ -9629,6 +9895,12 @@
           <t xml:space="preserve">  P4 — MEDIUM/LOW  |  Platform quality and research readiness</t>
         </is>
       </c>
+      <c r="B62" s="38" t="n"/>
+      <c r="C62" s="38" t="n"/>
+      <c r="D62" s="38" t="n"/>
+      <c r="E62" s="38" t="n"/>
+      <c r="F62" s="38" t="n"/>
+      <c r="G62" s="39" t="n"/>
     </row>
     <row r="63" ht="32" customHeight="1">
       <c r="A63" s="4" t="n">
@@ -9646,7 +9918,7 @@
       </c>
       <c r="D63" s="21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -9656,12 +9928,12 @@
       </c>
       <c r="F63" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>Log model/version, prompt template, selected context, retrieved sources, decision reasons, latency, tokens, failures, outcome links</t>
+          <t>AiInteractionLog.js is thorough (model/provider/promptSource/retrievalConfig/grounded/fallbackUsed/latencyMs/outputChars/score/confidenceScore) and GET /api/ai-tutor/admin/interaction-logs aggregates it -- but aiInteractionLogger.js is only called from 3 of ~15 AI-calling route files (video/ai-tutor/long-answer); most AI calls (lesson plans, exams, rubrics, reading/writing, learning paths, admin insights) are not logged. No frontend consumer of the aggregation endpoint either</t>
         </is>
       </c>
     </row>
@@ -9696,7 +9968,7 @@
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>Document every generation, embedding, speech, assessment, classification model with metrics, thresholds, privacy, cost, rollback rules</t>
+          <t>No model registry document found; CLAUDE.md itself notes model IDs "drift" and must be read from .env</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9988,7 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -9726,12 +9998,12 @@
       </c>
       <c r="F65" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>Build labeled relevance, grounding, citation, and cross-tenant leakage benchmarks</t>
+          <t>ai-service/tests/test_eval_live.py + tests/golden/golden_set.example.json is a real harness checking retrieval relevance, cross-tenant leakage (test_other_school_cannot_retrieve_material), and groundedness -- opt-in via RUN_AI_EVALS=1</t>
         </is>
       </c>
     </row>
@@ -9766,7 +10038,7 @@
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>Measure unsupported claims; require source-grounded answers for curriculum content</t>
+          <t>The eval harness above only keyword-matches expected content; no unsupported-claim/hallucination scoring exists</t>
         </is>
       </c>
     </row>
@@ -9796,12 +10068,12 @@
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>Replace critical in-process cron/fire-and-forget with retryable jobs, idempotency, and failure monitoring</t>
+          <t>backend/schedulers/spacedRepetitionCron.js uses node-cron with noOverlap:true and per-job try/catch isolation, but no retry/backoff, no dead-letter queue, no external job monitoring; also logs via console.error rather than the Pino logger convention</t>
         </is>
       </c>
     </row>
@@ -9821,7 +10093,7 @@
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -9831,12 +10103,12 @@
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>Add properly namespaced short-lived session/context/cache state only where it improves reliability</t>
+          <t>backend/utils/studentSubjectsCache.js uses Redis for versioned, scoped caching (org/school/campus/class/section) beyond rate-limiting/socket adapter</t>
         </is>
       </c>
     </row>
@@ -9871,7 +10143,7 @@
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>Track usage by capability, model, tenant, activity, and outcome without logging excessive student content</t>
+          <t>AiInteractionLog tracks latency/outputChars/citationCount/model/provider -- no token counts or cost fields</t>
         </is>
       </c>
     </row>
@@ -9901,12 +10173,12 @@
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>Add service-level metrics and safe user-visible fallback states</t>
+          <t>AiInteractionLog + admin aggregation endpoint is real backend telemetry, but no frontend consumer and no "AI unavailable" fallback UI found in AITutorHomeScreen.jsx</t>
         </is>
       </c>
     </row>
@@ -9941,7 +10213,7 @@
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>Add ethical assignment, exposure, consent/governance, treatment version, outcome, and exclusion records</t>
+          <t>No experiment-assignment model or exposure tracking found</t>
         </is>
       </c>
     </row>
@@ -9976,7 +10248,7 @@
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>Implement only after security and valid learning-outcome measurement exist</t>
+          <t>Depends on item 71; nothing exists yet</t>
         </is>
       </c>
     </row>
@@ -10011,7 +10283,7 @@
       </c>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>Evaluate efficacy, effectiveness, ethics, equity, environment, and science-of-learning alignment</t>
+          <t>No structured efficacy/effectiveness/ethics/equity/environment evaluation framework found</t>
         </is>
       </c>
     </row>
@@ -10046,7 +10318,7 @@
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>Measure review time, recommendation acceptance, overrides, decision quality, workload effects</t>
+          <t>No teacher review-time/override-rate tracking found</t>
         </is>
       </c>
     </row>
@@ -10066,7 +10338,7 @@
       </c>
       <c r="D75" s="23" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -10081,7 +10353,7 @@
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>Add structured, purpose-limited feedback linked to feature versions and outcomes</t>
+          <t>No feedback-collection model tied to feature versions found</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10145,12 +10417,22 @@
       </c>
       <c r="D2" s="27" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E2" s="27" t="inlineStr">
         <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>% Done</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>% At Least Started</t>
         </is>
       </c>
     </row>
@@ -10167,9 +10449,17 @@
         <v>10</v>
       </c>
       <c r="D3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -10185,14 +10475,22 @@
         <v>14</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" s="30" t="inlineStr">
-        <is>
-          <t>64%</t>
+        <v>2</v>
+      </c>
+      <c r="E4" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -10206,14 +10504,22 @@
         <v>4</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="33" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="E5" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
     </row>
@@ -10227,35 +10533,51 @@
         <v>8</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="30" t="inlineStr">
-        <is>
-          <t>62%</t>
+        <v>0</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="28" t="inlineStr">
         <is>
-          <t>5. Knowledge Graph</t>
+          <t>5. Knowledge Graph Engine</t>
         </is>
       </c>
       <c r="B7" s="29" t="n">
         <v>9</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" s="33" t="inlineStr">
-        <is>
-          <t>33%</t>
+        <v>4</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>89%</t>
         </is>
       </c>
     </row>
@@ -10269,14 +10591,22 @@
         <v>10</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="E8" s="33" t="inlineStr">
-        <is>
-          <t>40%</t>
+        <v>0</v>
+      </c>
+      <c r="E8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -10290,35 +10620,51 @@
         <v>5</v>
       </c>
       <c r="C9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" s="33" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="E9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>8. Gap Detection</t>
+          <t>8. Gap Detection Engine</t>
         </is>
       </c>
       <c r="B10" s="32" t="n">
         <v>5</v>
       </c>
       <c r="C10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" s="33" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="E10" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -10332,35 +10678,51 @@
         <v>4</v>
       </c>
       <c r="C11" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" s="33" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="E11" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="31" t="inlineStr">
         <is>
-          <t>10. Student Memory</t>
+          <t>10. Student Memory Engine</t>
         </is>
       </c>
       <c r="B12" s="32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="E12" s="33" t="inlineStr">
-        <is>
-          <t>33%</t>
+        <v>1</v>
+      </c>
+      <c r="E12" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
     </row>
@@ -10374,14 +10736,22 @@
         <v>9</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" s="30" t="inlineStr">
-        <is>
-          <t>67%</t>
+        <v>1</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>89%</t>
         </is>
       </c>
     </row>
@@ -10392,17 +10762,25 @@
         </is>
       </c>
       <c r="B14" s="32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="E14" s="33" t="inlineStr">
-        <is>
-          <t>42%</t>
+        <v>0</v>
+      </c>
+      <c r="E14" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -10413,17 +10791,25 @@
         </is>
       </c>
       <c r="B15" s="29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" s="33" t="inlineStr">
-        <is>
-          <t>36%</t>
+        <v>0</v>
+      </c>
+      <c r="E15" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -10437,14 +10823,22 @@
         <v>7</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="30" t="inlineStr">
-        <is>
-          <t>71%</t>
+        <v>0</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -10463,7 +10857,15 @@
       <c r="D17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10484,9 +10886,17 @@
       <c r="D18" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="30" t="inlineStr">
+      <c r="E18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>80%</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -10500,14 +10910,22 @@
         <v>4</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="30" t="inlineStr">
-        <is>
-          <t>50%</t>
+        <v>0</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -10521,14 +10939,22 @@
         <v>4</v>
       </c>
       <c r="C20" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" s="33" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="E20" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -10542,14 +10968,22 @@
         <v>8</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="E21" s="33" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="E21" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
     </row>
@@ -10560,17 +10994,25 @@
         </is>
       </c>
       <c r="B22" s="32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="30" t="inlineStr">
-        <is>
-          <t>86%</t>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>85%</t>
         </is>
       </c>
     </row>
@@ -10587,9 +11029,17 @@
         <v>3</v>
       </c>
       <c r="D23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="E23" s="30" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -10605,14 +11055,22 @@
         <v>8</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="E24" s="33" t="inlineStr">
-        <is>
-          <t>25%</t>
+        <v>1</v>
+      </c>
+      <c r="E24" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -10626,14 +11084,22 @@
         <v>14</v>
       </c>
       <c r="C25" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="E25" s="33" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -10644,17 +11110,25 @@
         </is>
       </c>
       <c r="B26" s="32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="E26" s="30" t="inlineStr">
-        <is>
-          <t>50%</t>
+        <v>5</v>
+      </c>
+      <c r="E26" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -10668,14 +11142,22 @@
         <v>5</v>
       </c>
       <c r="C27" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" s="33" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -10686,129 +11168,204 @@
         </is>
       </c>
       <c r="B28" s="35" t="n">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C28" s="35" t="n">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="D28" s="35" t="n">
-        <v>117</v>
-      </c>
-      <c r="E28" s="35" t="inlineStr">
-        <is>
-          <t>43%</t>
+        <v>24</v>
+      </c>
+      <c r="E28" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>93%</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="36" t="inlineStr">
         <is>
-          <t>P0 Critical Blockers — 15 items (0 done)</t>
+          <t>P0 Critical Items — 15 total: 9 Done, 4 Partial, 2 Not Started (was 0 done on 2026-08-17)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❌  AI-service authentication (FastAPI has zero auth)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  ❌  AI-service authentication (Not Started) — Zero auth on any of 12 ai-service FastAPI routers (admin/assessment/chat/documents/eval...</t>
+        </is>
+      </c>
+      <c r="B31" s="40" t="n"/>
+      <c r="C31" s="40" t="n"/>
+      <c r="D31" s="40" t="n"/>
+      <c r="E31" s="41" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❌  End-to-end tenant isolation (org/year missing from Qdrant)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  🔶  End-to-end tenant isolation (Partial) — Mongo (tenantPlugin.js) and Qdrant (school/class/section/academic_year filters) both ge...</t>
+        </is>
+      </c>
+      <c r="B32" s="40" t="n"/>
+      <c r="C32" s="40" t="n"/>
+      <c r="D32" s="40" t="n"/>
+      <c r="E32" s="41" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❌  Safe document ingestion (SSRF vulnerability)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  🔶  Safe document ingestion (SSRF fix) (Partial) — aiTutorRoutes.js explain-photo + videoUnderstandingRoutes.js both validate (https-only,...</t>
+        </is>
+      </c>
+      <c r="B33" s="40" t="n"/>
+      <c r="C33" s="40" t="n"/>
+      <c r="D33" s="40" t="n"/>
+      <c r="E33" s="41" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❌  Server-authoritative assessment (browser grading MCQs)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  ✅  Server-authoritative assessment (Done) — practiceRoutes.js /student/submit re-fetches questions+correctAnswer server-side and gr...</t>
+        </is>
+      </c>
+      <c r="B34" s="40" t="n"/>
+      <c r="C34" s="40" t="n"/>
+      <c r="D34" s="40" t="n"/>
+      <c r="E34" s="41" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❌  Canonical learning events (no immutable event log)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  ✅  Canonical learning events (Done) — MasteryEvent.js is genuinely append-only/immutable (blocks save on non-new docs + all u...</t>
+        </is>
+      </c>
+      <c r="B35" s="40" t="n"/>
+      <c r="C35" s="40" t="n"/>
+      <c r="D35" s="40" t="n"/>
+      <c r="E35" s="41" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❌  Real mastery model ($max never decreases; browser-writable)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  ✅  Real mastery model (Done) — masteryEventService::blendScore is a real EMA (previous*0.7+new*0.3, algorithmVersion m...</t>
+        </is>
+      </c>
+      <c r="B36" s="40" t="n"/>
+      <c r="C36" s="40" t="n"/>
+      <c r="D36" s="40" t="n"/>
+      <c r="E36" s="41" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❌  Concept and prerequisite model (no curriculum nodes)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  ✅  Concept and prerequisite model (Done) — CurriculumMap.js has real prerequisites:[String] edges per topic; gapDetectionEngine.js...</t>
+        </is>
+      </c>
+      <c r="B37" s="40" t="n"/>
+      <c r="C37" s="40" t="n"/>
+      <c r="D37" s="40" t="n"/>
+      <c r="E37" s="41" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❌  Misconception detection (no taxonomy, just wrong-answer counts)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  🔶  Misconception detection (Partial) — StudentMisconception.js has a real 5-value errorType taxonomy, evidence[], occurrence c...</t>
+        </is>
+      </c>
+      <c r="B38" s="40" t="n"/>
+      <c r="C38" s="40" t="n"/>
+      <c r="D38" s="40" t="n"/>
+      <c r="E38" s="41" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❌  Evidence-based recommendation engine (ephemeral, not persisted)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  ✅  Evidence-based recommendation engine (Done) — RecommendationEvent.js persists reason/explainability/lifecycle status (issued/accepted...</t>
+        </is>
+      </c>
+      <c r="B39" s="40" t="n"/>
+      <c r="C39" s="40" t="n"/>
+      <c r="D39" s="40" t="n"/>
+      <c r="E39" s="41" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❌  Complete adaptive feedback loop (no hint→retry→reassess cycle)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  ✅  Complete adaptive feedback loop (Done) — Verified chain: applyAssessment -&gt; masteryEngine.runWorkflowTriggers -&gt; gapDetectionEng...</t>
+        </is>
+      </c>
+      <c r="B40" s="40" t="n"/>
+      <c r="C40" s="40" t="n"/>
+      <c r="D40" s="40" t="n"/>
+      <c r="E40" s="41" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❌  Child-safety system (no distress/self-harm handling)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  ❌  Child-safety system (Not Started) — escalationService.js::assessWellbeing only checks mood/academicStress/socialEngagement/...</t>
+        </is>
+      </c>
+      <c r="B41" s="40" t="n"/>
+      <c r="C41" s="40" t="n"/>
+      <c r="D41" s="40" t="n"/>
+      <c r="E41" s="41" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❌  RAG isolation and citations (org/year missing; citations dropped)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  ✅  RAG isolation and citations (Done) — Retrieval filters by school_id/class_id/section_id/academic_year_id; citations (source_...</t>
+        </is>
+      </c>
+      <c r="B42" s="40" t="n"/>
+      <c r="C42" s="40" t="n"/>
+      <c r="D42" s="40" t="n"/>
+      <c r="E42" s="41" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❌  Teacher authorization enforcement (allocations not applied)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  ✅  Teacher authorization enforcement (Done) — buildTeacherAllocationScope used across teacherAnalyticsRoutes, aiTeacherRoutes, escala...</t>
+        </is>
+      </c>
+      <c r="B43" s="40" t="n"/>
+      <c r="C43" s="40" t="n"/>
+      <c r="D43" s="40" t="n"/>
+      <c r="E43" s="41" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❌  Remove fake intelligence (hardcoded goals/leaderboards)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  ✅  Remove fake intelligence (Done) — No hardcoded/Math.random fallback found in recommendation/mastery/analytics paths; 'wea...</t>
+        </is>
+      </c>
+      <c r="B44" s="40" t="n"/>
+      <c r="C44" s="40" t="n"/>
+      <c r="D44" s="40" t="n"/>
+      <c r="E44" s="41" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❌  Complete student-data deletion (only 5 collections deleted)</t>
+          <t xml:space="preserve">  🔶  Complete student-data deletion (Partial) — deleteSchoolCascade.js covers ~35 core ERP collections but no AI-era models (MasterySco...</t>
+        </is>
+      </c>
+      <c r="B45" s="40" t="n"/>
+      <c r="C45" s="40" t="n"/>
+      <c r="D45" s="40" t="n"/>
+      <c r="E45" s="41" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Re-audited 2026-09-11 against the current codebase (see Build Checklist / Feature Backlog Notes columns for full evidence)</t>
         </is>
       </c>
     </row>
